--- a/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G02-G04.xlsx
+++ b/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -567,22 +567,22 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Construye un modelo de las capas de la Tierra (corteza, manto y núcleo), las ordena por profundidad y explica que el interior del planeta está muy caliente.</t>
+          <t>Construye un modelo de las capas de la Tierra (corteza, manto y núcleo), las ordena por profundidad y compara su estado y temperatura.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Capas internas de la Tierra, Convección del manto y energía interna de la Tierra</t>
+          <t>Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Capas internas de la Tierra; prerrequisito: Convección del manto y energía interna de la Tierra (sin tema en la malla) de Energía geotérmica (2.°); se presenta en 2.° (acción 7) y se amplía aquí</t>
+          <t>fusión: ambos temas trabajan Capas internas de la Tierra</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Dos temas para el mismo concepto; la composición química de las capas es excesiva para 3.°. Unidos, introducen el calor interno de la Tierra. Libera el tema que paga el ciclo del agua (acción 2).</t>
+          <t>Dos temas para el mismo concepto; la composición química de las capas es excesiva para 3.°. Unirlos libera el tema que paga el ciclo del agua (acción 2).</t>
         </is>
       </c>
     </row>
@@ -625,12 +625,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>SG 5, UY 3 (Ciclo del agua; hoy en 7.°, G07-CIE-U5-5.1); prerrequisito: Ciclo del agua (hoy en 7.°) de Aguas subterráneas y acuíferos (3.°), confianza alta, brecha 4; prerrequisito: Ciclo del agua (hoy en 7.°) de Cuencas hidrográficas y aguas superficiales (3.°), confianza alta, brecha 4</t>
+          <t>AU 3, ENG 2, SG 5, UY 3 (Ciclo del agua; hoy en 7.°, G07-CIE-U5-5.1); prerrequisito: Hidrosfera: distribución del agua dulce y salada (3.°, G03-3.1, va antes); prerrequisito: Ciclo del agua (hoy en 7.°) de Aguas subterráneas y acuíferos y de Cuencas hidrográficas y aguas superficiales (3.°), confianza alta, brecha 4</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>El candidato sugiere 4.°, pero lagos, ríos y acuíferos ya se estudian en 3.° y lo necesitan. Va en 3.°, como Uruguay, al inicio de la unidad del agua. Se paga con la fusión 1.</t>
+          <t>Australia y Uruguay lo enseñan en 3.° e Inglaterra en 2.°; El Salvador, en 7.°. Va en 3.°, después de 3.1 (hidrosfera, su bloqueo) y antes de lagos, ríos y acuíferos, que lo necesitan. Se paga con la fusión 1.</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Los volcanes ocupan tres temas en 3.° (2.9, 2.10 y 2.11) y vuelven en 4.° (3.12 a 3.14). Unir las dos clasificaciones libera un tema para la acción 4.</t>
+          <t>Los volcanes ocupan tres temas en 3.° (2.9 a 2.11) y vuelven en 4.° (3.12 a 3.14). Unir las dos clasificaciones libera un tema para la acción 4.</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Simula con arena, piedras y agua cómo se desgastan, transportan y depositan los materiales y explica que el suelo se forma a partir de rocas desgastadas y restos de seres vivos.</t>
+          <t>Simula con arena, piedras y agua cómo las rocas se desgastan (meteorización), se transportan y se depositan, y explica que el suelo se forma de rocas desgastadas y restos de seres vivos descompuestos.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Erosión, transporte y sedimentación, Suelo: formación, componentes y tipos</t>
+          <t>Meteorización, Erosión, transporte y sedimentación, Suelo: formación, componentes y tipos</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Erosión, transporte y sedimentación (hoy en 5.°) de Ciclo de las rocas (3.°), confianza alta, brecha 2; prerrequisito: Erosión, transporte y sedimentación y Suelo: formación, componentes y tipos (hoy en 5.°) de Uso del suelo y su degradación (4.°), confianza alta</t>
+          <t>AU 2, ENG 2, UY 3, CO 6.5 (Suelo: formación, componentes y tipos; hoy en 5.°); prerrequisito: Meteorización (hoy en 5.°), bloqueo del suelo; se introduce primero en el mismo tema; prerrequisito: Productores, consumidores y descomponedores (Biología, 3.°); prerrequisito: Erosión, transporte y sedimentación (hoy en 5.°) de Ciclo de las rocas (3.°), confianza alta, brecha 2</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Los temas 2.8 de 3.° (formación de rocas) y 2.12 de 4.° (cultivos) necesitan erosión y suelo, que hoy llegan en 5.°. Un tema experimental los introduce antes. Se paga con la fusión 3.</t>
+          <t>Australia e Inglaterra enseñan el suelo en 2.°, pero su bloqueo (descomponedores) llega en 3.°. Va en 3.°, con la meteorización primero y antes de 2.8 (ciclo de las rocas). Se paga con la fusión 3.</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Indagación y simulación de los mismos fenómenos geológicos son dos momentos de una misma secuencia didáctica. La fusión libera un tema para el tiempo atmosférico (acción 6).</t>
+          <t>Indagación y simulación de los mismos fenómenos geológicos son dos momentos de una misma secuencia didáctica. Unirlos libera un tema para el tiempo atmosférico (acción 6).</t>
         </is>
       </c>
     </row>
@@ -805,36 +805,36 @@
       </c>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>3. Naturaleza y sus interacciones. (antes de 3.9)</t>
+          <t>2. Interacciones terrestres. (después de 2.14 y 2.15, sobre la atmósfera)</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>3.9. Medición y registro de las variables del tiempo atmosférico con instrumentos sencillos.</t>
+          <t>2.16. Medición y registro de las variables del tiempo atmosférico con instrumentos sencillos.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Mide durante varios días la temperatura, la lluvia y la dirección del viento con termómetro, pluviómetro y veleta (comerciales o construidos), registra los datos en una tabla y describe el tiempo de cada día.</t>
+          <t>Lee la temperatura en grados Celsius con un termómetro y mide la lluvia y el viento con pluviómetro y veleta (comerciales o construidos). Registra los datos varios días en una tabla y describe el tiempo de cada día.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Tiempo atmosférico y sus variables</t>
+          <t>Tiempo atmosférico y sus variables, Temperatura y escalas termométricas</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Tiempo atmosférico y sus variables (hoy en 7.°) de Ciclones tropicales y tormentas (4.°), confianza alta, brecha 3; prerrequisito: Tiempo atmosférico y sus variables (hoy en 7.°) de Clima: diferencia con el tiempo, tipos y factores (4.°), confianza alta, brecha 3; T4_27-E5.1 Uso de equipo en investigaciones de ciencias de la Tierra (reforzar: 1 tema, débil)</t>
+          <t>AU 2, ENG 2, CO 8.5 (Tiempo atmosférico y sus variables; hoy en 7.°, G07-CIE-U5-5.14 a 5.16); prerrequisito: La atmósfera y su composición (3.°, G03-2.14, va antes); prerrequisito: Temperatura y escalas termométricas (Física, hoy en 6.°); aquí solo la lectura del termómetro en °C; prerrequisito: Tiempo atmosférico y sus variables de Ciclones tropicales y tormentas y de Clima (4.°), confianza alta, brecha 3; T4_27-E5.1 Uso de equipo en investigaciones de ciencias de la Tierra (reforzar: 1 tema, débil)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Ciclones y climas tropicales se estudian en 4.° sin haber trabajado el tiempo atmosférico (7.°). El tema va al inicio del bloque hidrometeorológico y además refuerza el uso de instrumentos (E5.1). Se paga con la fusión 5.</t>
+          <t>Inglaterra y Australia lo enseñan en 2.°; El Salvador, en 7.°. No puede ir en 2.° porque la atmósfera llega en 3.°. En 3.° prepara climas y ciclones de 4.° y refuerza E5.1. Se paga con la fusión 5.</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G02-CIE-U2-2.3</t>
+          <t>G02-CIE-U2-2.7</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -868,81 +868,27 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2.3. Identificación de fuentes naturales de energía eléctrica y su clasificación en renovables y no renovables.</t>
+          <t>2.7. Identificación de recursos renovables y no renovables y de acciones sencillas para ahorrar energía eléctrica en el hogar y la escuela.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Nombra fuentes de energía de El Salvador (sol, viento, agua, calor de los volcanes y aguas termales, petróleo), reconoce que el interior de la Tierra está caliente y agrupa las fuentes en las que se renuevan y las que se agotan.</t>
+          <t>Agrupa recursos de su entorno (agua, sol, viento, árboles, petróleo, metales) en los que se renuevan y los que se agotan, y propone acciones para ahorrar energía eléctrica en casa y en la escuela.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Energía geotérmica, Fuentes de energía renovables y no renovables, Recursos naturales renovables y no renovables, Convección del manto y energía interna de la Tierra</t>
+          <t>Recursos naturales renovables y no renovables, Conservación de recursos, residuos y sostenibilidad, La energía y sus usos</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Recursos naturales renovables y no renovables (hoy en 7.° según candidatos) de Fuentes de energía renovables y no renovables (2.°), confianza alta, brecha 5; prerrequisito: Recursos naturales renovables y no renovables de Conservación de recursos, residuos y sostenibilidad (2.°), confianza alta, brecha 5; prerrequisito: Convección del manto y energía interna de la Tierra (sin tema en la malla) de Energía geotérmica (2.°), confianza alta; aquí solo como idea de calor interno, se amplía en 3.° (acción 1)</t>
+          <t>prerrequisito: Recursos naturales renovables y no renovables (hoy en 7.° según candidatos) de Conservación de recursos, residuos y sostenibilidad (2.°), confianza alta, brecha 5; prerrequisito: Recursos naturales renovables y no renovables de Fuentes de energía renovables y no renovables (2.°, hoy en Física), confianza alta, brecha 5</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Corrige sin gastar presupuesto dos secuencias invertidas: introduce recurso renovable y no renovable antes del ahorro de energía (2.7) y del descarte (6.7), y el calor interno de la Tierra antes de la geotermia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>G03-CIE-U2-2.15</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2. Interacciones terrestres.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2.15. Descripción de la composición del aire y de las características de las capas atmosféricas de la Tierra.</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Reconoce que el aire es una mezcla de gases (principalmente nitrógeno y oxígeno) y describe cómo cambian la temperatura y el aire con la altura en las capas de la atmósfera.</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>La atmósfera y su composición, Capas de la atmósfera y variación con la altitud</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>prerrequisito: La atmósfera y su composición (sin tema en la malla) de Capas de la atmósfera y variación con la altitud (3.°), confianza alta</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Las capas de la atmósfera se estudian sin haber visto de qué está hecho el aire, que no tiene tema en la malla. Se reformula el tema para introducir primero la composición, sin gastar presupuesto.</t>
+          <t>El tema 2.3, donde v1 hacía este ajuste, pasó a Física. Se reformula 2.7, el primer tema de la asignatura en 2.°, para introducir la idea de recurso renovable antes del ahorro de energía y del descarte de materiales (6.7).</t>
         </is>
       </c>
     </row>
@@ -1005,10 +951,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1028,10 +974,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1051,10 +997,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>

--- a/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G02-G04.xlsx
+++ b/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G02-G04.xlsx
@@ -625,12 +625,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>AU 3, ENG 2, SG 5, UY 3 (Ciclo del agua; hoy en 7.°, G07-CIE-U5-5.1); prerrequisito: Hidrosfera: distribución del agua dulce y salada (3.°, G03-3.1, va antes); prerrequisito: Ciclo del agua (hoy en 7.°) de Aguas subterráneas y acuíferos y de Cuencas hidrográficas y aguas superficiales (3.°), confianza alta, brecha 4</t>
+          <t>AU 3, ENG 2, JP 3, SG 5, UY 3 (Ciclo del agua; hoy en 7.°, G07-CIE-U5-5.1); prerrequisito: Hidrosfera: distribución del agua dulce y salada (3.°, G03-3.1, va antes); prerrequisito: Ciclo del agua (hoy en 7.°) de Aguas subterráneas y acuíferos y de Cuencas hidrográficas y aguas superficiales (3.°), confianza alta, brecha 4</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Australia y Uruguay lo enseñan en 3.° e Inglaterra en 2.°; El Salvador, en 7.°. Va en 3.°, después de 3.1 (hidrosfera, su bloqueo) y antes de lagos, ríos y acuíferos, que lo necesitan. Se paga con la fusión 1.</t>
+          <t>Australia, Japón y Uruguay lo enseñan en 3.° e Inglaterra en 2.°; El Salvador, en 7.°. Va en 3.°, después de 3.1 (hidrosfera, su bloqueo) y antes de lagos, ríos y acuíferos. Se paga con la fusión 1.</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>AU 2, ENG 2, UY 3, CO 6.5 (Suelo: formación, componentes y tipos; hoy en 5.°); prerrequisito: Meteorización (hoy en 5.°), bloqueo del suelo; se introduce primero en el mismo tema; prerrequisito: Productores, consumidores y descomponedores (Biología, 3.°); prerrequisito: Erosión, transporte y sedimentación (hoy en 5.°) de Ciclo de las rocas (3.°), confianza alta, brecha 2</t>
+          <t>AU 2, ENG 2, JP 3, UY 3, CO 6.5 (Suelo: formación, componentes y tipos; hoy en 5.°); prerrequisito: Meteorización (hoy en 5.°), bloqueo del suelo; se introduce primero en el mismo tema; prerrequisito: Productores, consumidores y descomponedores (Biología, 3.°); prerrequisito: Erosión, transporte y sedimentación (hoy en 5.°) de Ciclo de las rocas (3.°), confianza alta, brecha 2; prerrequisito: Erosión, transporte y sedimentación y Suelo: formación, componentes y tipos (hoy en 5.°) de Uso del suelo y su degradación (4.°), confianza alta, brecha 1</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Australia e Inglaterra enseñan el suelo en 2.°, pero su bloqueo (descomponedores) llega en 3.°. Va en 3.°, con la meteorización primero y antes de 2.8 (ciclo de las rocas). Se paga con la fusión 3.</t>
+          <t>Tres países de alto desempeño lo respaldan (AU y ENG en 2.°, JP en 3.°). Va en 3.° porque su bloqueo (descomponedores) llega en 3.°; meteorización primero, antes de 2.8 (ciclo de las rocas). Se paga con la fusión 3.</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>AU 2, ENG 2, CO 8.5 (Tiempo atmosférico y sus variables; hoy en 7.°, G07-CIE-U5-5.14 a 5.16); prerrequisito: La atmósfera y su composición (3.°, G03-2.14, va antes); prerrequisito: Temperatura y escalas termométricas (Física, hoy en 6.°); aquí solo la lectura del termómetro en °C; prerrequisito: Tiempo atmosférico y sus variables de Ciclones tropicales y tormentas y de Clima (4.°), confianza alta, brecha 3; T4_27-E5.1 Uso de equipo en investigaciones de ciencias de la Tierra (reforzar: 1 tema, débil)</t>
+          <t>AU 2, ENG 2, JP 3, CO 8.5 (Tiempo atmosférico y sus variables; hoy en 7.°, G07-CIE-U5-5.14 a 5.16); prerrequisito: La atmósfera y su composición (3.°, G03-2.14, va antes); prerrequisito: Temperatura y escalas termométricas (Física, hoy en 6.°); aquí solo la lectura del termómetro en °C; prerrequisito: Tiempo atmosférico y sus variables de Ciclones tropicales y tormentas y de Clima (4.°), confianza alta, brecha 3; T4_27-E5.1 Uso de equipo en investigaciones de ciencias de la Tierra (reforzar: 1 tema, débil)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Inglaterra y Australia lo enseñan en 2.°; El Salvador, en 7.°. No puede ir en 2.° porque la atmósfera llega en 3.°. En 3.° prepara climas y ciclones de 4.° y refuerza E5.1. Se paga con la fusión 5.</t>
+          <t>Inglaterra y Australia lo enseñan en 2.° y Japón en 3.°; El Salvador, en 7.°. No puede ir en 2.° porque la atmósfera llega en 3.°. Prepara climas y ciclones de 4.° y refuerza E5.1. Se paga con la fusión 5.</t>
         </is>
       </c>
     </row>

--- a/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G02-G04.xlsx
+++ b/asignaturas/ciencias_tierra_espacio/propuesta/Propuesta_Ciencias_tierra_espacio_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -889,6 +889,106 @@
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>El tema 2.3, donde v1 hacía este ajuste, pasó a Física. Se reformula 2.7, el primer tema de la asignatura en 2.°, para introducir la idea de recurso renovable antes del ahorro de energía y del descarte de materiales (6.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>G03-CIE-U2-2.6</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2. Interacciones terrestres.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>2.6. Identificación de rocas como elementos de uso común.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Identifica objetos de su casa y su comunidad hechos de roca (piedras de construcción, piedra de moler, grava) y los agrupa según la roca que usan, sin tratar todavía minerales ni minería.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>etiqueta secundaria (confianza media) «Recursos minerales y minería» en un tema de inventario de objetos de roca; prerrequisito: Minerales y sus propiedades (8.°) de Recursos minerales y minería, confianza alta, brecha 5</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>El tema es observacional: reconoce rocas en objetos cotidianos. No trabaja yacimientos, extracción ni impactos de la minería, que necesitan minerales (8.°). Se retira la etiqueta y se conserva «Tipos de rocas» como concepto principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>G04-CIE-U4-4.3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4. Sistema solar.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4.3. Representación de las propiedades físicas de la Luna y su movimiento alrededor de la Tierra.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Modela la formación de cráteres (altura de caída y tamaño del cráter), describe la superficie de la Luna y representa que gira alrededor de la Tierra.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>etiqueta secundaria (confianza media) «Mareas» en un tema cuya evidencia es el experimento de cráteres; prerrequisito: Gravedad y órbitas (sin tema en la malla) de Mareas, confianza alta</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>El tema trabaja las propiedades físicas de la Luna; la «interacción con la Tierra» en 4.° es su órbita, no la explicación gravitatoria de las mareas. Se retira la etiqueta; las mareas deben llegar después de gravedad y órbitas.</t>
         </is>
       </c>
     </row>
